--- a/shucle_report/삼호/20260101_20260325/report_삼호_20260101_20260325.xlsx
+++ b/shucle_report/삼호/20260101_20260325/report_삼호_20260101_20260325.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.01.01 ~ 03.25 | 비교기간: 2025.10.01 ~ 12.30 | 생성: 2026-03-26 13:09 | 차트: 148개</t>
+          <t>분석기간: 2026.01.01 ~ 03.25 | 비교기간: 2025.10.01 ~ 12.30 | 생성: 2026-03-26 14:48 | 차트: 148개</t>
         </is>
       </c>
     </row>
@@ -1830,17 +1830,17 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>-13.5</t>
+          <t>-9.6</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>평일 69.7명 (16% 감소)</t>
+          <t>평일 49.8명 (16% 감소)</t>
         </is>
       </c>
     </row>
@@ -1867,17 +1867,17 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>-28.9</t>
+          <t>-8.3</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>주말 47.7명 (38% 감소)</t>
+          <t>주말 13.6명 (38% 감소)</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>평일 23.8분 (5% 감소)</t>
+          <t>평일 17.0분 (5% 감소)</t>
         </is>
       </c>
     </row>
@@ -2344,17 +2344,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>주말 20.9분 (12% 감소)</t>
+          <t>주말 6.0분 (12% 감소)</t>
         </is>
       </c>
     </row>
